--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -995,6 +995,53 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>44.1%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>55.9%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2824</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>50.2%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2534</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -1003,42 +1003,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>72</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>29.5%</t>
         </is>
       </c>
     </row>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1042,6 +1042,53 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>41.1%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>58.9%</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>28.1%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25.6%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1089,6 +1089,53 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>30.3%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>22.3%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1136,6 +1136,53 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>70.6%</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>36.6%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1183,6 +1183,53 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>35.5%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>64.5%</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2178</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>38.8%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1230,6 +1230,53 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>24.1%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>75.9%</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1469</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>26.2%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1592</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>28.4%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1277,6 +1277,53 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>29.1%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>70.9%</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>35.3%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1077</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1324,6 +1324,53 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2393</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>42.6%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>11.7%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1371,6 +1371,53 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>52.7%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>47.3%</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1780</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>31.7%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>17.7%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1418,6 +1418,53 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>48.0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>52.0%</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2781</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>49.6%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1465,6 +1465,53 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>56.2%</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>31.9%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1252</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>22.3%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1512,6 +1512,53 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1569</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>28.0%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1490</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>26.6%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1559,6 +1559,53 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>84.4%</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1383</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>24.7%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>32.3%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1606,6 +1606,53 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>40.4%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>59.6%</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>39.1%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1653,6 +1653,53 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>21.9%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>78.1%</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2226</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>39.7%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1318</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>23.5%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1700,6 +1700,53 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>23.8%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>76.2%</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2286</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>19.5%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1747,6 +1747,53 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>32.8%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>67.2%</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2521</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>44.9%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>16.3%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1794,6 +1794,53 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>33.6%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>66.4%</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>34.3%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1841,6 +1841,53 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16.2%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>83.8%</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1637</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>29.2%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1699</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30.3%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1888,6 +1888,53 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1873</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>18.6%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1935,6 +1935,53 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>22.7%</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>77.3%</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>24.4%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>26.8%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1982,6 +1982,53 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>58.8%</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>41.2%</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2042</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>24.5%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2029,6 +2029,53 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>28.7%</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>71.3%</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1126</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20.1%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2089</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>37.2%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2076,53 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>40.9%</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>59.1%</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1428</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>25.4%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1491</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>26.6%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2123,6 +2123,53 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>33.9%</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>66.1%</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2169</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>38.6%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1633</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>29.1%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2170,6 +2170,53 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>35.5%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>21.8%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2217,6 +2217,53 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>54.0%</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>46.0%</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>33.5%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1757</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>31.3%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finviz_breadth.xlsx
+++ b/finviz_breadth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2264,6 +2264,53 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>48.7%</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>51.3%</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>27.5%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2220</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>39.5%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
